--- a/output/2026-09-14/enriched_analysis.xlsx
+++ b/output/2026-09-14/enriched_analysis.xlsx
@@ -5873,19 +5873,19 @@
         <v>119.71</v>
       </c>
       <c r="J30" t="n">
-        <v>111.43</v>
+        <v>111.01</v>
       </c>
       <c r="K30" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="L30" t="n">
         <v>73.48</v>
       </c>
       <c r="M30" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="N30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.207</v>
+        <v>0.198</v>
       </c>
       <c r="Q30" t="n">
         <v>227</v>
@@ -5935,10 +5935,10 @@
         <v>11.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>111.7162906724512</v>
+        <v>111.3431590909091</v>
       </c>
       <c r="AE30" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="AK30" t="n">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="AL30" t="n">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="AM30" t="n">
         <v>11</v>
@@ -6827,7 +6827,7 @@
         <v>2.16</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y35" t="b">
         <v>0</v>
@@ -11801,19 +11801,19 @@
         <v>119.71</v>
       </c>
       <c r="D30" t="n">
-        <v>111.43</v>
+        <v>111.01</v>
       </c>
       <c r="E30" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="F30" t="n">
         <v>73.48</v>
       </c>
       <c r="G30" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>

--- a/output/2026-09-14/enriched_analysis.xlsx
+++ b/output/2026-09-14/enriched_analysis.xlsx
@@ -1157,27 +1157,27 @@
         <v>70.79000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>70.39</v>
+        <v>70.28</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="L4" t="n">
         <v>72.56999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="N4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>10-09-2026</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.75</v>
+        <v>0.822</v>
       </c>
       <c r="Q4" t="n">
         <v>208</v>
@@ -1219,10 +1219,10 @@
         <v>55.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>70.38777512080679</v>
+        <v>70.28138945546696</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -1246,53 +1246,53 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>10-09-2026</t>
         </is>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL4" t="n">
         <v>28</v>
       </c>
       <c r="AM4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>2371760</v>
+        <v>3856745</v>
       </c>
       <c r="AT4" t="n">
-        <v>5168760</v>
+        <v>6653745</v>
       </c>
       <c r="AU4" t="n">
-        <v>15571254</v>
+        <v>17056239</v>
       </c>
       <c r="AV4" t="n">
-        <v>15571254</v>
+        <v>17056239</v>
       </c>
       <c r="AW4" t="n">
-        <v>15571254</v>
+        <v>17056239</v>
       </c>
       <c r="AX4" t="n">
-        <v>2371760</v>
+        <v>3856745</v>
       </c>
       <c r="AY4" t="n">
-        <v>15571254</v>
+        <v>17056239</v>
       </c>
       <c r="AZ4" t="n">
         <v>1</v>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.1523</v>
+        <v>0.2261</v>
       </c>
     </row>
     <row r="5">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery Limited</t>
+          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -10891,23 +10891,23 @@
         <v>70.79000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>70.39</v>
+        <v>70.28</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F4" t="n">
         <v>72.56999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>10-09-2026</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery Limited</t>
+          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C22" t="n">

--- a/output/2026-09-14/enriched_analysis.xlsx
+++ b/output/2026-09-14/enriched_analysis.xlsx
@@ -1125,16 +1125,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>INDORAMA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1142,87 +1142,87 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>70.79000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="J4" t="n">
-        <v>70.28</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7</v>
+        <v>14.3</v>
       </c>
       <c r="L4" t="n">
-        <v>72.56999999999999</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>1.71</v>
+        <v>3.14</v>
       </c>
       <c r="N4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.822</v>
+        <v>0.139</v>
       </c>
       <c r="Q4" t="n">
-        <v>208</v>
+        <v>2259</v>
       </c>
       <c r="R4" t="n">
-        <v>8.859999999999999</v>
+        <v>19.8</v>
       </c>
       <c r="S4" t="n">
-        <v>17</v>
+        <v>-3</v>
       </c>
       <c r="T4" t="n">
-        <v>27.97</v>
+        <v>62</v>
       </c>
       <c r="U4" t="n">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="V4" t="n">
-        <v>2.73</v>
+        <v>1.29</v>
       </c>
       <c r="W4" t="n">
-        <v>13.7</v>
+        <v>15.8</v>
       </c>
       <c r="X4" t="n">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="Y4" t="b">
         <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
-        <v>59.94</v>
+        <v>58.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>52.03</v>
+        <v>45.68</v>
       </c>
       <c r="AC4" t="n">
-        <v>55.3</v>
+        <v>153.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>70.28138945546696</v>
+        <v>75.6844038997483</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.7</v>
+        <v>14.3</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
@@ -1231,68 +1231,68 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="AK4" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="AL4" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="AM4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AP4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AR4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AS4" t="n">
-        <v>3856745</v>
+        <v>31393588</v>
       </c>
       <c r="AT4" t="n">
-        <v>6653745</v>
+        <v>31393588</v>
       </c>
       <c r="AU4" t="n">
-        <v>17056239</v>
+        <v>31393588</v>
       </c>
       <c r="AV4" t="n">
-        <v>17056239</v>
+        <v>31393588</v>
       </c>
       <c r="AW4" t="n">
-        <v>17056239</v>
+        <v>31393588</v>
       </c>
       <c r="AX4" t="n">
-        <v>3856745</v>
+        <v>31393588</v>
       </c>
       <c r="AY4" t="n">
-        <v>17056239</v>
+        <v>31393588</v>
       </c>
       <c r="AZ4" t="n">
         <v>1</v>
@@ -1301,18 +1301,18 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.2261</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INDORAMA</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1324,157 +1324,157 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F5" t="n">
         <v>19</v>
       </c>
       <c r="G5" t="n">
+        <v>17</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>70.79000000000001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>74.56</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>72.56999999999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="N5" t="n">
+        <v>16</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>208</v>
+      </c>
+      <c r="R5" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="S5" t="n">
+        <v>17</v>
+      </c>
+      <c r="T5" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="U5" t="n">
+        <v>17</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="W5" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Y5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>59.94</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>52.03</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>74.56036417156598</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
         <v>25</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>75.68000000000001</v>
-      </c>
-      <c r="K5" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>74.84999999999999</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>09-09-2026</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2259</v>
-      </c>
-      <c r="R5" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>62</v>
-      </c>
-      <c r="U5" t="n">
-        <v>77</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W5" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Y5" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>58.83</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>45.68</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>153.7</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>75.6844038997483</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Fresh</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Early Accumulation</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>08-09-2026</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>09-09-2026</t>
-        </is>
-      </c>
-      <c r="AK5" t="n">
-        <v>1</v>
-      </c>
       <c r="AL5" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="AM5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN5" t="n">
         <v>5</v>
       </c>
-      <c r="AN5" t="n">
-        <v>2</v>
-      </c>
       <c r="AO5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AP5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="AR5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>31393588</v>
+        <v>5341730</v>
       </c>
       <c r="AT5" t="n">
-        <v>31393588</v>
+        <v>8138730</v>
       </c>
       <c r="AU5" t="n">
-        <v>31393588</v>
+        <v>18541224</v>
       </c>
       <c r="AV5" t="n">
-        <v>31393588</v>
+        <v>18541224</v>
       </c>
       <c r="AW5" t="n">
-        <v>31393588</v>
+        <v>18541224</v>
       </c>
       <c r="AX5" t="n">
-        <v>31393588</v>
+        <v>5341730</v>
       </c>
       <c r="AY5" t="n">
-        <v>31393588</v>
+        <v>18541224</v>
       </c>
       <c r="AZ5" t="n">
         <v>1</v>
@@ -1483,7 +1483,7 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1</v>
+        <v>0.2881</v>
       </c>
     </row>
     <row r="6">
@@ -3123,12 +3123,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>Alembic Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G15" t="n">
         <v>21</v>
@@ -3152,165 +3152,165 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>523.8</v>
+        <v>810.95</v>
       </c>
       <c r="J15" t="n">
-        <v>505.37</v>
+        <v>746.01</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>62.09</v>
+        <v>69.61</v>
       </c>
       <c r="M15" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="N15" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.192</v>
+        <v>0.013</v>
       </c>
       <c r="Q15" t="n">
-        <v>899</v>
+        <v>15940</v>
       </c>
       <c r="R15" t="n">
-        <v>8.84</v>
+        <v>20.2</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="T15" t="n">
-        <v>30</v>
+        <v>346</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="V15" t="n">
-        <v>14.66</v>
+        <v>10.02</v>
       </c>
       <c r="W15" t="n">
-        <v>14.4</v>
+        <v>12.3</v>
       </c>
       <c r="X15" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="Y15" t="b">
         <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AA15" t="n">
-        <v>494.52</v>
+        <v>821.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>488.06</v>
+        <v>787.34</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.8</v>
+        <v>13.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>505.3685224651855</v>
+        <v>746.006474564212</v>
       </c>
       <c r="AE15" t="n">
-        <v>3.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>17-06-2026</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="AK15" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="AL15" t="n">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="AM15" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="AN15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AS15" t="n">
-        <v>8548580</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>12970627</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>17310388</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>17310388</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>17310388</v>
+        <v>20970242</v>
       </c>
       <c r="AX15" t="n">
-        <v>8548580</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>17310388</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA15" t="n">
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.4938</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals Limited</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3322,157 +3322,153 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="F16" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
         <v>21</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I16" t="n">
-        <v>810.95</v>
+        <v>14</v>
       </c>
       <c r="J16" t="n">
-        <v>746.01</v>
+        <v>12.79</v>
       </c>
       <c r="K16" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="L16" t="n">
-        <v>69.61</v>
+        <v>69.12</v>
       </c>
       <c r="M16" t="n">
         <v>2.1</v>
       </c>
       <c r="N16" t="n">
+        <v>21</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>395</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1274</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-61</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="n">
+        <v>-98</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Y16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>18-06-2026</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>15940</v>
-      </c>
-      <c r="R16" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>16</v>
-      </c>
-      <c r="T16" t="n">
-        <v>346</v>
-      </c>
-      <c r="U16" t="n">
-        <v>88</v>
-      </c>
-      <c r="V16" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="W16" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="Y16" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>821.04</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>787.34</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>13.8</v>
-      </c>
       <c r="AD16" t="n">
-        <v>746.006474564212</v>
+        <v>12.74905965615859</v>
       </c>
       <c r="AE16" t="n">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>17-06-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AK16" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AL16" t="n">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="AM16" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AR16" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>4045537</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>7167901</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>14063235</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>21553624</v>
       </c>
       <c r="AW16" t="n">
-        <v>20970242</v>
+        <v>21553624</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>4045537</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>14063235</v>
       </c>
       <c r="AZ16" t="n">
         <v>1</v>
@@ -3481,22 +3477,22 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>0.2877</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3504,34 +3500,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>611.1</v>
+        <v>523.8</v>
       </c>
       <c r="J17" t="n">
-        <v>614.84</v>
+        <v>505.37</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6</v>
+        <v>3.6</v>
       </c>
       <c r="L17" t="n">
-        <v>64.68000000000001</v>
+        <v>62.09</v>
       </c>
       <c r="M17" t="n">
-        <v>4.52</v>
+        <v>1.73</v>
       </c>
       <c r="N17" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -3539,52 +3535,52 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.401</v>
+        <v>0.192</v>
       </c>
       <c r="Q17" t="n">
-        <v>1128</v>
+        <v>899</v>
       </c>
       <c r="R17" t="n">
-        <v>57.4</v>
+        <v>8.84</v>
       </c>
       <c r="S17" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.11</v>
+        <v>30</v>
       </c>
       <c r="U17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.07000000000000001</v>
+        <v>14.66</v>
       </c>
       <c r="W17" t="n">
-        <v>1.58</v>
+        <v>14.4</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Y17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="n">
-        <v>-110</v>
+        <v>14</v>
       </c>
       <c r="AA17" t="n">
-        <v>576.3099999999999</v>
+        <v>494.52</v>
       </c>
       <c r="AB17" t="n">
-        <v>512.6</v>
+        <v>488.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>21.8</v>
+        <v>20.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>614.8401686157193</v>
+        <v>505.3685224651855</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.6</v>
+        <v>3.6</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
@@ -3603,7 +3599,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -3612,49 +3608,49 @@
         </is>
       </c>
       <c r="AK17" t="n">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="AL17" t="n">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="AM17" t="n">
         <v>3</v>
       </c>
       <c r="AN17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AP17" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="AS17" t="n">
-        <v>2486819</v>
+        <v>8548580</v>
       </c>
       <c r="AT17" t="n">
-        <v>4715920</v>
+        <v>12970627</v>
       </c>
       <c r="AU17" t="n">
-        <v>21426404</v>
+        <v>17310388</v>
       </c>
       <c r="AV17" t="n">
-        <v>21768420</v>
+        <v>17310388</v>
       </c>
       <c r="AW17" t="n">
-        <v>41877891</v>
+        <v>17310388</v>
       </c>
       <c r="AX17" t="n">
-        <v>2486819</v>
+        <v>8548580</v>
       </c>
       <c r="AY17" t="n">
-        <v>21426404</v>
+        <v>17310388</v>
       </c>
       <c r="AZ17" t="n">
         <v>2</v>
@@ -3663,22 +3659,22 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.1161</v>
+        <v>0.4938</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3686,157 +3682,157 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H18" t="n">
         <v>-1</v>
       </c>
       <c r="I18" t="n">
-        <v>217.12</v>
+        <v>611.1</v>
       </c>
       <c r="J18" t="n">
-        <v>170.45</v>
+        <v>614.84</v>
       </c>
       <c r="K18" t="n">
-        <v>27.4</v>
+        <v>-0.6</v>
       </c>
       <c r="L18" t="n">
-        <v>67.54000000000001</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>0.26</v>
+        <v>4.52</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.089</v>
+        <v>0.401</v>
       </c>
       <c r="Q18" t="n">
-        <v>292</v>
+        <v>1128</v>
       </c>
       <c r="R18" t="n">
-        <v>31.3</v>
+        <v>57.4</v>
       </c>
       <c r="S18" t="n">
+        <v>21</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="U18" t="n">
+        <v>23</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-110</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>576.3099999999999</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>512.6</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>614.8401686157193</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>12-06-2026</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="AK18" t="n">
+        <v>91</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>94</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP18" t="n">
         <v>24</v>
       </c>
-      <c r="T18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-31</v>
-      </c>
-      <c r="V18" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="W18" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>179.47</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>162.42</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>170.4518641810919</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>4</v>
-      </c>
       <c r="AQ18" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="AR18" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2486819</v>
       </c>
       <c r="AT18" t="n">
-        <v>5120374</v>
+        <v>4715920</v>
       </c>
       <c r="AU18" t="n">
-        <v>5120374</v>
+        <v>21426404</v>
       </c>
       <c r="AV18" t="n">
-        <v>5120374</v>
+        <v>21768420</v>
       </c>
       <c r="AW18" t="n">
-        <v>5120374</v>
+        <v>41877891</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>2486819</v>
       </c>
       <c r="AY18" t="n">
-        <v>5120374</v>
+        <v>21426404</v>
       </c>
       <c r="AZ18" t="n">
         <v>2</v>
@@ -3845,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>0.1161</v>
       </c>
     </row>
     <row r="19">
@@ -4031,16 +4027,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4048,162 +4044,166 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H20" t="n">
         <v>-1</v>
       </c>
       <c r="I20" t="n">
-        <v>14</v>
+        <v>217.12</v>
       </c>
       <c r="J20" t="n">
-        <v>12.69</v>
+        <v>170.45</v>
       </c>
       <c r="K20" t="n">
-        <v>10.3</v>
+        <v>27.4</v>
       </c>
       <c r="L20" t="n">
-        <v>69.12</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>1.92</v>
+        <v>0.26</v>
       </c>
       <c r="N20" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.486</v>
+        <v>0.089</v>
       </c>
       <c r="Q20" t="n">
-        <v>395</v>
+        <v>292</v>
       </c>
       <c r="R20" t="n">
-        <v>1274</v>
+        <v>31.3</v>
       </c>
       <c r="S20" t="n">
-        <v>-61</v>
-      </c>
-      <c r="T20" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.87</v>
+      </c>
       <c r="U20" t="n">
-        <v>-98</v>
+        <v>-31</v>
       </c>
       <c r="V20" t="n">
-        <v>0.01</v>
+        <v>3.36</v>
       </c>
       <c r="W20" t="n">
-        <v>2.46</v>
+        <v>4.96</v>
       </c>
       <c r="X20" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="b">
         <v>1</v>
       </c>
-      <c r="Z20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>2.97</v>
+      </c>
       <c r="AA20" t="n">
-        <v>11.69</v>
+        <v>179.47</v>
       </c>
       <c r="AB20" t="n">
-        <v>13.34</v>
+        <v>162.42</v>
       </c>
       <c r="AC20" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>170.4518641810919</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Late — Poor Entry</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>5120374</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>5120374</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>5120374</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>5120374</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>5120374</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>2</v>
       </c>
-      <c r="AD20" t="n">
-        <v>12.64449812963585</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>Fresh</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>10-08-2026</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>10-09-2026</t>
-        </is>
-      </c>
-      <c r="AK20" t="n">
-        <v>31</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>35</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2218898</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>5341262</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>12236596</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>19726985</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>19726985</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>2218898</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>12236596</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1</v>
-      </c>
       <c r="BA20" t="n">
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0.1813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -6645,7 +6645,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="X34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="b">
         <v>1</v>
@@ -6827,7 +6827,7 @@
         <v>2.16</v>
       </c>
       <c r="X35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="b">
         <v>0</v>
@@ -10879,70 +10879,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>INDORAMA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>70.79000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="D4" t="n">
-        <v>70.28</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7</v>
+        <v>14.3</v>
       </c>
       <c r="F4" t="n">
-        <v>72.56999999999999</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>1.71</v>
+        <v>3.14</v>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INDORAMA</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>86.5</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>75.68000000000001</v>
+        <v>74.56</v>
       </c>
       <c r="E5" t="n">
-        <v>14.3</v>
+        <v>-5.1</v>
       </c>
       <c r="F5" t="n">
-        <v>74.84999999999999</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>3.14</v>
+        <v>1.85</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
@@ -11264,101 +11264,101 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>Alembic Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>523.8</v>
+        <v>810.95</v>
       </c>
       <c r="D15" t="n">
-        <v>505.37</v>
+        <v>746.01</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>62.09</v>
+        <v>69.61</v>
       </c>
       <c r="G15" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="H15" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals Limited</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>810.95</v>
+        <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>746.01</v>
+        <v>12.79</v>
       </c>
       <c r="E16" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="F16" t="n">
-        <v>69.61</v>
+        <v>69.12</v>
       </c>
       <c r="G16" t="n">
         <v>2.1</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>611.1</v>
+        <v>523.8</v>
       </c>
       <c r="D17" t="n">
-        <v>614.84</v>
+        <v>505.37</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6</v>
+        <v>3.6</v>
       </c>
       <c r="F17" t="n">
-        <v>64.68000000000001</v>
+        <v>62.09</v>
       </c>
       <c r="G17" t="n">
-        <v>4.52</v>
+        <v>1.73</v>
       </c>
       <c r="H17" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -11369,35 +11369,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>217.12</v>
+        <v>611.1</v>
       </c>
       <c r="D18" t="n">
-        <v>170.45</v>
+        <v>614.84</v>
       </c>
       <c r="E18" t="n">
-        <v>27.4</v>
+        <v>-0.6</v>
       </c>
       <c r="F18" t="n">
-        <v>67.54000000000001</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.26</v>
+        <v>4.52</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
@@ -11439,35 +11439,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14</v>
+        <v>217.12</v>
       </c>
       <c r="D20" t="n">
-        <v>12.69</v>
+        <v>170.45</v>
       </c>
       <c r="E20" t="n">
-        <v>10.3</v>
+        <v>27.4</v>
       </c>
       <c r="F20" t="n">
-        <v>69.12</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>1.92</v>
+        <v>0.26</v>
       </c>
       <c r="H20" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
     </row>
@@ -12764,7 +12764,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -12774,7 +12774,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -12804,7 +12804,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
